--- a/exports/KFINTECH_full_report.xlsx
+++ b/exports/KFINTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.59</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>331.1</v>
+        <v>316.35</v>
       </c>
       <c r="I2" t="n">
         <v>323.8164685138511</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.73</v>
+        <v>-8.98</v>
       </c>
       <c r="L2" t="n">
-        <v>5.63</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>2.33</v>
+        <v>4.26</v>
       </c>
       <c r="O2" t="n">
         <v>-1.94</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.91</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45006.55208333334</v>
+        <v>45007.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>285.7</v>
+        <v>292.25</v>
       </c>
       <c r="I3" t="n">
         <v>290.4925283218153</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K3" t="n">
-        <v>9.69</v>
+        <v>7.62</v>
       </c>
       <c r="L3" t="n">
         <v>6.15</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45012.55208333334</v>
+        <v>45013.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>279</v>
+        <v>275.15</v>
       </c>
       <c r="I4" t="n">
         <v>275.4531383561261</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.53</v>
+        <v>-5.85</v>
       </c>
       <c r="L4" t="n">
-        <v>5.65</v>
+        <v>6.14</v>
       </c>
       <c r="M4" t="n">
         <v>4.93</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>296.4</v>
+        <v>313.15</v>
       </c>
       <c r="I5" t="n">
         <v>298.9783202738819</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.72</v>
+        <v>-13.81</v>
       </c>
       <c r="L5" t="n">
-        <v>8.9</v>
+        <v>15.17</v>
       </c>
       <c r="M5" t="n">
         <v>1.27</v>
       </c>
       <c r="N5" t="n">
-        <v>2.83</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
         <v>-0.68</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45054.38541666666</v>
+        <v>45054.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>314.95</v>
+        <v>304.9</v>
       </c>
       <c r="I6" t="n">
         <v>308.3953606606733</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.57</v>
+        <v>-2.63</v>
       </c>
       <c r="L6" t="n">
         <v>4.6</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>326.15</v>
+        <v>339.45</v>
       </c>
       <c r="I7" t="n">
         <v>335.0995864101311</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.97</v>
+        <v>-11.33</v>
       </c>
       <c r="L7" t="n">
-        <v>9.869999999999999</v>
+        <v>12.94</v>
       </c>
       <c r="M7" t="n">
         <v>1.27</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>348.7</v>
+        <v>342</v>
       </c>
       <c r="I8" t="n">
         <v>343.0387759439533</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>2.72</v>
+        <v>0.75</v>
       </c>
       <c r="L8" t="n">
         <v>5.13</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>346</v>
+        <v>374.5</v>
       </c>
       <c r="I9" t="n">
         <v>367.5969227609215</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.17</v>
+        <v>-9.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.91</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
         <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
         <v>-2.29</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>455.3</v>
+        <v>448.8</v>
       </c>
       <c r="I10" t="n">
         <v>449.1521312336729</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>109.1666666666667</v>
+        <v>110</v>
       </c>
       <c r="K10" t="n">
-        <v>21.58</v>
+        <v>19.84</v>
       </c>
       <c r="L10" t="n">
         <v>7.34</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.45</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>478.35</v>
+        <v>482.8</v>
       </c>
       <c r="I11" t="n">
         <v>480.0881450034526</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.58</v>
+        <v>-7.58</v>
       </c>
       <c r="L11" t="n">
         <v>8.630000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.92</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45272.55208333334</v>
+        <v>45273.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>515</v>
+        <v>500.95</v>
       </c>
       <c r="I12" t="n">
         <v>509.2368592621325</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>6.67</v>
+        <v>3.76</v>
       </c>
       <c r="L12" t="n">
         <v>2.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>513.65</v>
+        <v>518.4</v>
       </c>
       <c r="I13" t="n">
         <v>516.9226143516532</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.54</v>
+        <v>-3.48</v>
       </c>
       <c r="L13" t="n">
         <v>9.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.66</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>684</v>
+        <v>646.55</v>
       </c>
       <c r="I14" t="n">
         <v>661.4623986004627</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>31.94</v>
+        <v>24.72</v>
       </c>
       <c r="L14" t="n">
         <v>1.16</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>630.5</v>
+        <v>638.25</v>
       </c>
       <c r="I15" t="n">
         <v>633.3150859295076</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>2.48</v>
+        <v>1.28</v>
       </c>
       <c r="L15" t="n">
         <v>5.75</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.86</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>742.1</v>
+        <v>702.6</v>
       </c>
       <c r="I16" t="n">
         <v>737.7434404920643</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K16" t="n">
-        <v>16.27</v>
+        <v>10.08</v>
       </c>
       <c r="L16" t="n">
         <v>7.25</v>
@@ -1353,7 +1544,7 @@
         <v>3.86</v>
       </c>
       <c r="N16" t="n">
-        <v>3.57</v>
+        <v>8.91</v>
       </c>
       <c r="O16" t="n">
         <v>0.5600000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.7</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45474.38541666666</v>
+        <v>45474.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>727.9</v>
+        <v>730.55</v>
       </c>
       <c r="I17" t="n">
         <v>730.5318231893154</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.6</v>
+        <v>-3.98</v>
       </c>
       <c r="L17" t="n">
         <v>6.3</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.23</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1009.1</v>
+        <v>995.1</v>
       </c>
       <c r="I18" t="n">
         <v>999.2635097247667</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>66</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>38.13</v>
+        <v>36.21</v>
       </c>
       <c r="L18" t="n">
         <v>4.32</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.52</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1009.75</v>
+        <v>1079.05</v>
       </c>
       <c r="I19" t="n">
         <v>1054.438664170708</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.47</v>
+        <v>-8.44</v>
       </c>
       <c r="L19" t="n">
-        <v>7.93</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>1.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>13.52</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1030.9</v>
+        <v>1014</v>
       </c>
       <c r="I20" t="n">
         <v>1029.024478067849</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.46</v>
+        <v>-6.03</v>
       </c>
       <c r="L20" t="n">
         <v>7.97</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.56</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45581.38541666666</v>
+        <v>45581.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1092.05</v>
+        <v>1108.9</v>
       </c>
       <c r="I21" t="n">
         <v>1097.644648576145</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.7</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>10.49</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1035</v>
+        <v>989.15</v>
       </c>
       <c r="I22" t="n">
         <v>1016.397963578386</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.66</v>
+        <v>-10.8</v>
       </c>
       <c r="L22" t="n">
-        <v>6.89</v>
+        <v>11.62</v>
       </c>
       <c r="M22" t="n">
         <v>-0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.61</v>
+        <v>4.73</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>13.25</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1038.7</v>
+        <v>1046</v>
       </c>
       <c r="I23" t="n">
         <v>1044.098741887915</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.01</v>
+        <v>-5.75</v>
       </c>
       <c r="L23" t="n">
         <v>6.15</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>1400</v>
+        <v>1378.45</v>
       </c>
       <c r="I24" t="n">
         <v>1396.560019216292</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>64.83333333333333</v>
+        <v>65</v>
       </c>
       <c r="K24" t="n">
-        <v>33.84</v>
+        <v>31.78</v>
       </c>
       <c r="L24" t="n">
         <v>8.550000000000001</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1174.9</v>
+        <v>1221.8</v>
       </c>
       <c r="I25" t="n">
         <v>1193.848375350776</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>14.77</v>
+        <v>11.36</v>
       </c>
       <c r="L25" t="n">
         <v>1.94</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>13.46</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1154.05</v>
+        <v>1040.6</v>
       </c>
       <c r="I26" t="n">
         <v>1085.719869646469</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.55</v>
+        <v>-14.83</v>
       </c>
       <c r="L26" t="n">
-        <v>6.33</v>
+        <v>15.28</v>
       </c>
       <c r="M26" t="n">
         <v>0.02</v>
       </c>
       <c r="N26" t="n">
-        <v>5.79</v>
+        <v>9.58</v>
       </c>
       <c r="O26" t="n">
         <v>4.26</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>20.78</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>939</v>
+        <v>974.55</v>
       </c>
       <c r="I27" t="n">
         <v>956.0386122882348</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
-        <v>9.76</v>
+        <v>6.35</v>
       </c>
       <c r="L27" t="n">
         <v>10.99</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.32</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1029.9</v>
+        <v>1024.95</v>
       </c>
       <c r="I28" t="n">
         <v>1026.306543603557</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>5.68</v>
+        <v>5.17</v>
       </c>
       <c r="L28" t="n">
         <v>3.48</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.53</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1053</v>
+        <v>1125.9</v>
       </c>
       <c r="I29" t="n">
         <v>1075.008846571358</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.74</v>
+        <v>-9.85</v>
       </c>
       <c r="L29" t="n">
-        <v>5.75</v>
+        <v>11.85</v>
       </c>
       <c r="M29" t="n">
         <v>3.56</v>
       </c>
       <c r="N29" t="n">
-        <v>4.27</v>
+        <v>4.84</v>
       </c>
       <c r="O29" t="n">
         <v>0.5</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.65</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45779.38541666666</v>
+        <v>45779.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1138.6</v>
+        <v>1120</v>
       </c>
       <c r="I30" t="n">
         <v>1129.554542053172</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.13</v>
+        <v>-0.52</v>
       </c>
       <c r="L30" t="n">
         <v>5.28</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.95</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1075</v>
+        <v>1141.6</v>
       </c>
       <c r="I31" t="n">
         <v>1124.195019291368</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>4.02</v>
+        <v>-1.93</v>
       </c>
       <c r="L31" t="n">
         <v>3.57</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.2</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1259.3</v>
+        <v>1226.9</v>
       </c>
       <c r="I32" t="n">
         <v>1243.104778963364</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>10.31</v>
+        <v>7.47</v>
       </c>
       <c r="L32" t="n">
         <v>6.64</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1056.6</v>
+        <v>1091.3</v>
       </c>
       <c r="I33" t="n">
         <v>1090.491453277812</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K33" t="n">
-        <v>13.88</v>
+        <v>11.05</v>
       </c>
       <c r="L33" t="n">
         <v>2.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1135.1</v>
+        <v>1090</v>
       </c>
       <c r="I34" t="n">
         <v>1101.288004687366</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>4.01</v>
+        <v>-0.12</v>
       </c>
       <c r="L34" t="n">
         <v>3.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.38</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45940.55208333334</v>
+        <v>45943.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1075</v>
+        <v>1132</v>
       </c>
       <c r="I35" t="n">
         <v>1095.459017035085</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>1.38</v>
+        <v>-3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>4.14</v>
+        <v>4.39</v>
       </c>
       <c r="M35" t="n">
         <v>1.46</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>6.84</v>
       </c>
       <c r="O35" t="n">
         <v>-5.23</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.99</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1131</v>
+        <v>1105.4</v>
       </c>
       <c r="I36" t="n">
         <v>1113.786377700751</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.09</v>
+        <v>-2.35</v>
       </c>
       <c r="L36" t="n">
         <v>4.12</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.43</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1082</v>
+        <v>1096.2</v>
       </c>
       <c r="I37" t="n">
         <v>1082.268729805295</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K37" t="n">
-        <v>2.12</v>
+        <v>0.83</v>
       </c>
       <c r="L37" t="n">
         <v>2.76</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.69</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1050.9</v>
+        <v>1042.4</v>
       </c>
       <c r="I38" t="n">
         <v>1044.514069428003</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.13</v>
+        <v>-4.91</v>
       </c>
       <c r="L38" t="n">
         <v>5.4</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.27</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1026.1</v>
+        <v>1038.8</v>
       </c>
       <c r="I39" t="n">
         <v>1033.149636643938</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>1.56</v>
+        <v>0.35</v>
       </c>
       <c r="L39" t="n">
         <v>3.39</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46080.38541666666</v>
+        <v>46080.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>958.5</v>
+        <v>956.9</v>
       </c>
       <c r="I40" t="n">
         <v>958.3180247920777</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.73</v>
+        <v>-7.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7.89</v>
+        <v>8.07</v>
       </c>
       <c r="M40" t="n">
         <v>0.2</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.21</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46127.55208333334</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>935.95</v>
+        <v>946.85</v>
       </c>
       <c r="I41" t="n">
         <v>946.4940987542016</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>2.19</v>
+        <v>1.05</v>
       </c>
       <c r="L41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="M41" t="n">
         <v>5.06</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>979</v>
+        <v>915.3</v>
       </c>
       <c r="I42" t="n">
         <v>938.5991534899932</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>3.4</v>
+        <v>-3.33</v>
       </c>
       <c r="L42" t="n">
-        <v>0.61</v>
+        <v>5.76</v>
       </c>
       <c r="M42" t="n">
-        <v>0.16</v>
+        <v>4.37</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>8.19</v>
       </c>
       <c r="O42" t="n">
         <v>2.14</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46171.38541666666</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>853.2</v>
+        <v>858</v>
       </c>
       <c r="I43" t="n">
         <v>855.7792064988835</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>6.78</v>
+        <v>6.26</v>
       </c>
       <c r="L43" t="n">
         <v>6.74</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>820.65</v>
+        <v>802.3</v>
       </c>
       <c r="I44" t="n">
         <v>809.4623220525837</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.35</v>
+        <v>-6.49</v>
       </c>
       <c r="L44" t="n">
-        <v>4.95</v>
+        <v>6.6</v>
       </c>
       <c r="M44" t="n">
         <v>1.28</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.47</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46189.38541666666</v>
+        <v>46189.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>849.9</v>
+        <v>863</v>
       </c>
       <c r="I45" t="n">
         <v>857.4820864152983</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.93</v>
+        <v>-7.57</v>
       </c>
       <c r="L45" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="M45" t="n">
         <v>2.11</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.65</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>864.65</v>
+        <v>848</v>
       </c>
       <c r="I46" t="n">
         <v>861.2176516594643</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K46" t="n">
-        <v>0.19</v>
+        <v>-1.74</v>
       </c>
       <c r="L46" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="M46" t="n">
         <v>0.5600000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>904.4</v>
+        <v>924.95</v>
       </c>
       <c r="I47" t="n">
         <v>905.7565805495619</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.65</v>
+        <v>-9.07</v>
       </c>
       <c r="L47" t="n">
-        <v>7.4</v>
+        <v>9.08</v>
       </c>
       <c r="M47" t="n">
         <v>0.45</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.91</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46227.38541666666</v>
+        <v>46227.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>869.55</v>
+        <v>859</v>
       </c>
       <c r="I48" t="n">
         <v>864.9871055761604</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.99</v>
+        <v>-7.13</v>
       </c>
       <c r="L48" t="n">
         <v>7.5</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.61</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>859</v>
+        <v>932.2</v>
       </c>
       <c r="I49" t="n">
         <v>907.1792971932374</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-8.52</v>
       </c>
       <c r="L49" t="n">
-        <v>1.34</v>
+        <v>8.73</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>10.37</v>
       </c>
       <c r="O49" t="n">
         <v>-1.6</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.31</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>925</v>
+        <v>924.2</v>
       </c>
       <c r="I50" t="n">
         <v>924.9932512894657</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.77</v>
+        <v>-0.86</v>
       </c>
       <c r="L50" t="n">
         <v>7.53</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.08</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>864.1</v>
+        <v>881.15</v>
       </c>
       <c r="I51" t="n">
         <v>874.0142405726624</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K51" t="n">
-        <v>6.5</v>
+        <v>4.66</v>
       </c>
       <c r="L51" t="n">
         <v>0.93</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.34</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>869.4</v>
+        <v>845.25</v>
       </c>
       <c r="I52" t="n">
         <v>848.336259257962</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.33</v>
+        <v>-4.07</v>
       </c>
       <c r="L52" t="n">
-        <v>1.67</v>
+        <v>4.08</v>
       </c>
       <c r="M52" t="n">
         <v>0.28</v>
       </c>
       <c r="N52" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="O52" t="n">
         <v>2.77</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>829.7</v>
+        <v>879.65</v>
       </c>
       <c r="I53" t="n">
         <v>857.2382532013421</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>1.84</v>
+        <v>-4.07</v>
       </c>
       <c r="L53" t="n">
-        <v>3.5</v>
+        <v>5.02</v>
       </c>
       <c r="M53" t="n">
-        <v>0.36</v>
+        <v>2.56</v>
       </c>
       <c r="N53" t="n">
-        <v>3.72</v>
+        <v>5.44</v>
       </c>
       <c r="O53" t="n">
         <v>-2.01</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3522,6 +4169,12 @@
       <c r="Q54" t="n">
         <v>2</v>
       </c>
+      <c r="R54" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5250,7 +5903,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -5260,7 +5913,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.1</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7">
@@ -5270,7 +5923,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109.2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
@@ -5280,7 +5933,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -5290,7 +5943,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5300,7 +5953,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -5310,7 +5963,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -5320,7 +5973,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -5330,7 +5983,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.3</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -5340,7 +5993,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.79</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="15">
@@ -5350,7 +6003,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.85</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="16">
@@ -5360,7 +6013,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.73</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="17">
@@ -5370,7 +6023,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.13</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="18">
@@ -5380,7 +6033,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="19">
@@ -5390,7 +6043,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.38</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="20">
@@ -5400,7 +6053,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.64</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="21">
@@ -5410,7 +6063,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.99</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="22">
@@ -5420,7 +6073,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -5430,7 +6083,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -5440,7 +6093,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="25">
@@ -5460,7 +6113,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5470,7 +6123,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.88</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="28">
@@ -5480,7 +6133,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
